--- a/artfynd/A 21006-2024 artfynd.xlsx
+++ b/artfynd/A 21006-2024 artfynd.xlsx
@@ -8693,10 +8693,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117722408</v>
+        <v>117722411</v>
       </c>
       <c r="B62" t="n">
-        <v>100007</v>
+        <v>78856</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8705,25 +8705,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222771</v>
+        <v>133</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Brun lundlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Bacidia polychroa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Th.Fr.) Körb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8733,10 +8733,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>683692</v>
+        <v>683677</v>
       </c>
       <c r="R62" t="n">
-        <v>6665106</v>
+        <v>6665151</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -8779,6 +8779,11 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>lönn</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -8795,10 +8800,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117722411</v>
+        <v>117722408</v>
       </c>
       <c r="B63" t="n">
-        <v>78856</v>
+        <v>100007</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8807,25 +8812,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>133</v>
+        <v>222771</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brun lundlav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bacidia polychroa</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Th.Fr.) Körb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8835,10 +8840,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>683677</v>
+        <v>683692</v>
       </c>
       <c r="R63" t="n">
-        <v>6665151</v>
+        <v>6665106</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -8881,11 +8886,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>lönn</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">

--- a/artfynd/A 21006-2024 artfynd.xlsx
+++ b/artfynd/A 21006-2024 artfynd.xlsx
@@ -8696,7 +8696,7 @@
         <v>117722411</v>
       </c>
       <c r="B62" t="n">
-        <v>78856</v>
+        <v>78858</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>117722408</v>
       </c>
       <c r="B63" t="n">
-        <v>100007</v>
+        <v>100009</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>

--- a/artfynd/A 21006-2024 artfynd.xlsx
+++ b/artfynd/A 21006-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AZ90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074389</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106141573</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106141824</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074369</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,6 +1278,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074415</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1351,6 +1381,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142015</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1459,6 +1494,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142873</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1561,6 +1601,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117722411</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1684,6 +1729,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72857219</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1809,6 +1859,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/220756</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1932,6 +1987,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72876032</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2051,6 +2111,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72876126</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2174,6 +2239,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72909820</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2295,6 +2365,11 @@
       <c r="AY15" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72913727</t>
         </is>
       </c>
     </row>
@@ -2399,6 +2474,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074381</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2515,6 +2595,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116351195</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2639,6 +2724,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72856802</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2763,6 +2853,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72876170</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2887,6 +2982,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72879055</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3011,6 +3111,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72913747</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3135,6 +3240,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80454985</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3263,6 +3373,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80650216</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3384,6 +3499,11 @@
       <c r="AY24" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80650460</t>
         </is>
       </c>
     </row>
@@ -3488,6 +3608,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074363</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3590,6 +3715,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074398</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3692,6 +3822,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074422</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3834,6 +3969,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72879005</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3972,6 +4112,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72913943</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4120,6 +4265,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80650355</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4262,6 +4412,11 @@
       <c r="AY31" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80650395</t>
         </is>
       </c>
     </row>
@@ -4366,6 +4521,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074357</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4464,6 +4624,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142008</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4572,6 +4737,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142220</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4680,6 +4850,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142800</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4813,6 +4988,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72876066</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4946,6 +5126,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72879101</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5079,6 +5264,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72913721</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5219,6 +5409,11 @@
       <c r="AY39" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72857052</t>
         </is>
       </c>
     </row>
@@ -5337,6 +5532,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82007284</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5466,6 +5666,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72865357</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5604,6 +5809,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72875224</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5742,6 +5952,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72878878</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5884,6 +6099,11 @@
       <c r="AY44" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80650363</t>
         </is>
       </c>
     </row>
@@ -6002,6 +6222,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82005608</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6110,6 +6335,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142172</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6224,6 +6454,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72875159</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6358,6 +6593,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72875981</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6492,6 +6732,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72878893</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6626,6 +6871,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72913953</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6761,6 +7011,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80649892</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6894,6 +7149,11 @@
       <c r="AY52" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80649933</t>
         </is>
       </c>
     </row>
@@ -7012,6 +7272,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82005594</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7140,6 +7405,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72875231</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7269,6 +7539,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72876023</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7382,6 +7657,11 @@
       <c r="AY56" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80650475</t>
         </is>
       </c>
     </row>
@@ -7485,6 +7765,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074374</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7583,6 +7868,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142016</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7720,6 +8010,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72865402</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7847,6 +8142,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72876198</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7965,6 +8265,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72913842</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8104,6 +8409,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80650039</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8241,6 +8551,11 @@
       <c r="AY63" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80650386</t>
         </is>
       </c>
     </row>
@@ -8368,6 +8683,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82005394</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8493,6 +8813,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82005960</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8594,6 +8919,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074355</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8692,6 +9022,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142012</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8805,6 +9140,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142153</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8903,6 +9243,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142009</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9011,6 +9356,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142796</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9138,6 +9488,11 @@
       <c r="AY71" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80454870</t>
         </is>
       </c>
     </row>
@@ -9242,6 +9597,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074400</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9361,6 +9721,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72875316</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9485,6 +9850,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80650314</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9604,6 +9974,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72875168</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9723,6 +10098,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72876127</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9842,6 +10222,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72913847</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9961,6 +10346,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80649867</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10085,6 +10475,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80650321</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10193,6 +10588,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106141549</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10312,6 +10712,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72875175</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10431,6 +10836,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80649847</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10546,6 +10956,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72913732</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10665,6 +11080,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80649856</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10789,6 +11209,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80650328</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10908,6 +11333,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72875185</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11022,6 +11452,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72876208</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11139,6 +11574,11 @@
       <c r="AY88" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80649840</t>
         </is>
       </c>
     </row>
@@ -11247,6 +11687,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82005309</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11344,8 +11789,104 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117722408</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>